--- a/05-self-assessment/first-day-questionnaires.xlsx
+++ b/05-self-assessment/first-day-questionnaires.xlsx
@@ -1834,7 +1834,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Not what you studied - what you've genuinely used, even a little. A "Never" here isn't a problem. A hidden one is - see the "What this changes" tab.</t>
+          <t>Not what you studied - what you've genuinely used, even a little. A "Never" here isn't a problem. A hidden one is. Each one changes what we do about it.</t>
         </is>
       </c>
     </row>
